--- a/Result/checksun_type/機械設備之沖壓零組件.xlsx
+++ b/Result/checksun_type/機械設備之沖壓零組件.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>28.13</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>28.19</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>28.74</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>28.19</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>28.74</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>594.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>320.8</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>320.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>413.6</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>545.42</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>545.42</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-39.43512646178118</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>594</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>594.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>28.05</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>28.2</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>28.77</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>28.77</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>313.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>386.0</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>386</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>430.7</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>534.72</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>534.72</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-62.04088280504749</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>313</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>313.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>28.05</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>28.21</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>28.8</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>28.21</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>28.8</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>174.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>379.6</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>379.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>501.4</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>542.68</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>542.6799999999999</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-62.01193176667624</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>174</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>174.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>28.09</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>28.22</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>28.83</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>28.22</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>28.83</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>196.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>407.0</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>407</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>535.3</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>539.84</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>539.84</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-44.86300414876456</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>196</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>196.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>28.15</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>28.24</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>28.86</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>28.24</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>28.86</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>327.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>538.0</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>538</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>561.3</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>535.94</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>535.9400000000001</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-21.1194288321492</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>327</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>327.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>28.14</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>28.25</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>28.88</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>28.25</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>28.88</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>920.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>506.4</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>506.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>701.5</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>544.3</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>544.3</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-0.4814844929788933</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>920</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>920.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>28.19</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>28.28</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>28.92</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>28.28</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>28.92</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>281.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>475.4</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>475.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>666.5</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>528.9</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>528.9</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-34.51722527655784</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>281</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>281.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>28.21</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>28.29</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>28.95</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>28.29</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>28.95</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>311.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>623.2</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>623.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>681.0</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>531.98</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>531.98</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-13.44266835036512</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>311</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>311.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>28.22</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>28.3</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>28.98</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>28.98</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>851.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>663.6</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>663.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>664.2</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>583.44</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>583.4400000000001</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>13.92965112813749</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>851</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>851.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>28.23</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>28.32</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>29.0</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>28.32</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>29</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>169.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>584.6</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>584.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>608.1</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>573.54</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>573.54</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-5.321665728577841</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>169</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>169.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>28.25</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>28.36</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>29.04</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>28.36</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>29.04</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>765.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>896.6</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>896.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>641.2</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>574.94</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>574.9400000000001</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>40.4379411092782</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>765</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>765.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5667,11 +5601,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
           <t>2459</t>
@@ -5853,41 +5783,37 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AN13" t="inlineStr">
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AP13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AS13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AT13" t="inlineStr">
         <is>
           <t>0</t>
@@ -5908,20 +5834,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>0</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>0</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5860,10 @@
           <t>0</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>0</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6029,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6213,11 @@
           <t>32.36</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>33.57</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>36.62</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>33.57</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>36.62</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6264,16 @@
           <t>403535423.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>568945866.2</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>568945866.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>551325175.1</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>652100733.04</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>652100733.04</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6290,10 @@
           <t>-64629376.5640012</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>403535423</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>403535423.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6459,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6643,11 @@
           <t>32.41</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>33.75</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>36.78</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>33.75</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>36.78</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6694,16 @@
           <t>363440217.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>575528949.6</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>575528949.6</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>594264436.4</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>657290966.96</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>657290966.96</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6720,10 @@
           <t>-58722927.5542357</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>363440217</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>363440217.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6889,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7073,11 @@
           <t>32.3</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>33.94</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>36.93</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>33.94</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>36.93</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7124,16 @@
           <t>451484020.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>575978704.8</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>575978704.8</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>641378457.8</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>656768454.26</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>656768454.26</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7150,10 @@
           <t>-43891980.91334808</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>451484020</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>451484020.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7319,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7503,11 @@
           <t>32.09</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>34.14</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>37.07</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>34.14</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>37.07</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7554,16 @@
           <t>569640781.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>620997783.6</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>620997783.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>705807978.8</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>655783883.94</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>655783883.9400001</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7580,10 @@
           <t>-30570608.14374614</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>569640781</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>569640781.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7749,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7933,11 @@
           <t>32.14</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>34.4</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>37.2</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>37.2</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7984,16 @@
           <t>1056628890.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>631631786.8</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>631631786.8</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>709807982.0</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>651233510.34</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>651233510.34</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8010,10 @@
           <t>-23107921.14632392</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>1056628890</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>1056628890.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8179,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8363,11 @@
           <t>32.12</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>34.62</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>37.31</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>34.62</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>37.31</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8414,16 @@
           <t>436450840.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>533704484.0</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>533704484</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>667262298.9</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>638216857.76</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>638216857.76</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8440,10 @@
           <t>-63798954.21620893</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>436450840</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>436450840.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8609,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8793,11 @@
           <t>32.35</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>34.95</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>37.46</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>37.46</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8844,16 @@
           <t>365688993.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>612999923.2</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>612999923.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>705359369.1</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>635887126.76</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>635887126.76</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8870,10 @@
           <t>-53202819.16546595</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>365688993</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>365688993.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9039,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9223,11 @@
           <t>32.81</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>35.28</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>37.61</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>35.28</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>37.61</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9274,16 @@
           <t>676579414.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>706778210.8</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>706778210.8</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>768838281.6</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>633235828.68</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>633235828.6799999</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9300,10 @@
           <t>-28583756.22992349</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>676579414</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>676579414.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9469,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9653,11 @@
           <t>33.39</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>35.56</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>37.76</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>35.56</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>37.76</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9704,16 @@
           <t>622810797.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>790618174.0</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>790618174</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>763691422.1</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>627286041.56</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>627286041.5599999</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9730,10 @@
           <t>-25702505.84950864</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>622810797</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>622810797.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9899,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10083,11 @@
           <t>34.07</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>35.84</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>37.9</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>35.84</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>37.9</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10134,16 @@
           <t>566992376.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>787984177.2</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>787984177.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>817890552.4</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>622376486.36</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>622376486.36</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10160,10 @@
           <t>-14907563.99000478</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>566992376</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>566992376.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10329,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10513,11 @@
           <t>34.47</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>36.09</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>38.03</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>36.09</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>38.03</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10564,16 @@
           <t>832928036.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>800820113.8</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>800820113.8</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>848956198.4</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>625070436.22</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>625070436.22</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10590,10 @@
           <t>7026739.630357981</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>832928036</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>832928036.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10759,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10943,11 @@
           <t>48.27</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>52.89</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>58.67</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>52.89</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>58.67</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10994,16 @@
           <t>533.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>4716.4</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>4716.4</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>3793.0</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>5834.36</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>5834.36</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11020,10 @@
           <t>-842.1280039432459</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>533</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>533.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11189,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11373,11 @@
           <t>47.73999999999999</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>53.57</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>58.94</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>53.57</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>58.94</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11424,16 @@
           <t>1493.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>4966.0</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>4966</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>3996.4</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>6021.16</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>6021.16</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11450,10 @@
           <t>-597.790131482544</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>1493</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>1493.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11619,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11803,11 @@
           <t>47.51</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>54.26</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>59.28</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>54.26</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>59.28</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11854,16 @@
           <t>1172.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>5624.4</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>5624.4</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>4371.8</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>6064.78</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>6064.78</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11880,10 @@
           <t>-330.2435232714515</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>1172</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>1172.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12049,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12233,11 @@
           <t>47.91</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>55.07</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>59.64</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>55.07</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>59.64</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12284,16 @@
           <t>18036.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>5852.8</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>5852.8</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>4334.8</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>6105.66</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>6105.66</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12310,10 @@
           <t>98.15318571837724</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>18036</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>18036.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12479,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12663,11 @@
           <t>48.7</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>55.87</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>60.04</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>55.87</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>60.04</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12714,16 @@
           <t>2348.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>2553.6</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>2553.6</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>3005.0</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>5804.76</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>5804.76</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12740,10 @@
           <t>-1100.214129500383</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>2348</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>2348.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12909,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13093,11 @@
           <t>49.23</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>56.6</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>60.42</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>60.42</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13144,16 @@
           <t>1781.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>2869.6</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>2869.6</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>4065.6</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>5830.72</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>5830.72</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13170,10 @@
           <t>-1092.016932330739</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>1781</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>1781.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13339,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13523,11 @@
           <t>50.13</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>57.3</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>60.8</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>57.3</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>60.8</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13574,16 @@
           <t>4785.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>3026.8</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>3026.8</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>6040.2</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>5817.18</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>5817.18</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13600,10 @@
           <t>-980.5560459337212</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>4785</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>4785.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13769,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13953,11 @@
           <t>51.06</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>57.87</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>61.17</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>57.87</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>61.17</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14004,16 @@
           <t>2314.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>3119.2</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>3119.2</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>6480.8</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>5796.92</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>5796.92</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14030,10 @@
           <t>-1108.163492297492</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>2314</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>2314.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14199,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14383,11 @@
           <t>51.72000000000001</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>58.33</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>61.48</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>58.33</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>61.48</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14434,16 @@
           <t>1540.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>2816.8</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>2816.8</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>8089.9</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>5943.54</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>5943.54</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14460,10 @@
           <t>-986.1325766636837</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>1540</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>1540.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14629,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14813,11 @@
           <t>52.38</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>58.74</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>61.78</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>58.74</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>61.78</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14864,16 @@
           <t>3928.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>3456.4</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>3456.4</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>9910.5</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>6081.78</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>6081.78</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14890,10 @@
           <t>-693.6551051631113</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>3928</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>3928.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15059,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15243,11 @@
           <t>53.66</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>59.12</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>62.13</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>59.12</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>62.13</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15294,16 @@
           <t>2567.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>5261.6</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>5261.6</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>11365.7</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>6269.82</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>6269.82</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15320,10 @@
           <t>-506.913892120755</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>2567</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>2567.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15489,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15673,11 @@
           <t>26.48</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>26.62</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>26.55</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>26.62</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>26.55</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15724,16 @@
           <t>7839.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>10068.4</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>10068.4</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>11722.6</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>8701.0</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>8701</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15750,10 @@
           <t>-616.6244144460488</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>7839</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>7839.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15919,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16103,11 @@
           <t>26.39</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>26.57</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>26.57</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>26.57</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>26.57</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16154,16 @@
           <t>6654.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>9000.2</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>9000.200000000001</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>13423.5</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>8700.2</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>8700.200000000001</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16180,10 @@
           <t>-392.1957297596437</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>6654</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>6654.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16349,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16533,11 @@
           <t>26.42</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>26.52</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>26.6</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>26.52</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>26.6</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16584,16 @@
           <t>18736.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>9117.0</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>9117</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>16178.4</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>9053.86</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>9053.860000000001</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16610,10 @@
           <t>69.3879529980677</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>18736</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>18736.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16779,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16963,11 @@
           <t>26.74</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>26.46</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>26.67</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>26.46</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>26.67</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17014,16 @@
           <t>3431.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>8104.0</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>8104</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>15889.0</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>9028.56</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>9028.559999999999</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17040,10 @@
           <t>-568.1849270979947</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>3431</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>3431.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17209,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17393,11 @@
           <t>27.04</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>26.39</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>26.72</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>26.39</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>26.72</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17444,16 @@
           <t>13682.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>10946.2</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>10946.2</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>17756.9</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>9401.94</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>9401.940000000001</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17470,10 @@
           <t>181.1104201611324</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>13682</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>13682.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17639,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17823,11 @@
           <t>27.2</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>26.29</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>26.72</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>26.29</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>26.72</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17874,16 @@
           <t>2498.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>13376.8</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>13376.8</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>17119.1</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>9431.78</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>9431.780000000001</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17900,10 @@
           <t>146.7426869541323</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>2498</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>2498.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18069,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18253,11 @@
           <t>27.63</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>26.24</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>26.76</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>26.24</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>26.76</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18304,16 @@
           <t>7238.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>17846.8</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>17846.8</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>17384.7</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>9631.6</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>9631.6</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18330,10 @@
           <t>1290.690829267198</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>7238</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>7238.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18499,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18683,11 @@
           <t>27.98</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>26.17</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>26.8</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>26.17</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>26.8</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18734,16 @@
           <t>13671.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>23239.8</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>23239.8</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>17089.8</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>9614.48</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>9614.48</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18760,10 @@
           <t>2370.949217240606</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>13671</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>13671.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18929,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19113,11 @@
           <t>27.89</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>26.08</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>26.82</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>26.08</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>26.82</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19164,16 @@
           <t>17642.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>23674.0</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>23674</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>16654.5</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>9529.58</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>9529.58</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19190,10 @@
           <t>3140.248728015453</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>17642</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>17642.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19359,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19543,11 @@
           <t>27.65</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>25.97</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>26.82</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>25.97</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>26.82</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19594,16 @@
           <t>25835.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>24567.6</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>24567.6</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>15300.0</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>9486.36</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>9486.360000000001</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19620,10 @@
           <t>3701.632003121827</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>25835</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>25835.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19789,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19973,11 @@
           <t>27.24</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>25.84</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>26.84</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>25.84</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>26.84</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20024,16 @@
           <t>24848.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>20861.4</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>20861.4</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>13072.2</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>9151.38</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>9151.379999999999</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20050,10 @@
           <t>3493.585538876581</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>24848</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>24848.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20219,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20403,11 @@
           <t>53.48</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>48.7</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>43.68</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>43.68</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20454,16 @@
           <t>3512622548.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>6095469315.0</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>6095469315</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>9544851503.2</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>3663541757.9</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>3663541757.9</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20480,10 @@
           <t>98808707.88450241</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>3512622548</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>3512622548.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20649,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20833,11 @@
           <t>54.02</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>48.25</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>43.41</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>48.25</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>43.41</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20884,16 @@
           <t>6744255965.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>6936487304.4</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>6936487304.4</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>10032139013.4</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>3632131847.42</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>3632131847.42</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20910,10 @@
           <t>468208784.7071676</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>6744255965</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>6744255965.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21079,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21263,11 @@
           <t>55.0</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>47.74</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>43.12</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>47.74</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>43.12</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21314,16 @@
           <t>4850127005.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>8366597065.8</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>8366597065.8</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>9915210649.5</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>3525171118.12</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>3525171118.12</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21340,10 @@
           <t>632955000.321434</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>4850127005</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>4850127005.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21509,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21693,11 @@
           <t>55.34</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>47.15</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>42.8</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>47.15</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>42.8</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21744,16 @@
           <t>4661687858.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>9917900867.8</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>9917900867.799999</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>9646311981.3</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>3483979320.62</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>3483979320.62</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21770,10 @@
           <t>1048643589.758906</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>4661687858</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>4661687858.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21939,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22123,11 @@
           <t>55.96</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>46.69</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>42.52</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>46.69</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>42.52</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22174,16 @@
           <t>10708653199.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>11555043688.4</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>11555043688.4</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>9440522375.4</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>3413291777.02</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>3413291777.02</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22200,10 @@
           <t>1625222783.642477</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>10708653199</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>10708653199.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22369,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22553,11 @@
           <t>55.4</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>45.98</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>42.16</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>45.98</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>42.16</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22604,16 @@
           <t>7717712495.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>12994233691.4</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>12994233691.4</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>8470087592.9</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>3233128694.92</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>3233128694.92</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22630,10 @@
           <t>1742974531.810349</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>7717712495</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>7717712495.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22799,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22983,11 @@
           <t>54.6</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>45.39</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>41.86</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>45.39</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>41.86</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23034,16 @@
           <t>13894804772.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>13127790722.4</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>13127790722.4</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>7823899971.0</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>3109382048.22</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>3109382048.22</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23060,10 @@
           <t>2169400157.056937</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>13894804772</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>13894804772.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23229,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23413,11 @@
           <t>52.2</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>44.62</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>41.5</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>44.62</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>41.5</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23464,16 @@
           <t>12606646015.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>11463824233.2</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>11463824233.2</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>6558502593.2</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>2879764455.78</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>2879764455.78</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23490,10 @@
           <t>2039269729.264316</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>12606646015</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>12606646015.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23659,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23843,11 @@
           <t>49.55</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>43.9</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>41.17</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>41.17</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23894,16 @@
           <t>12847401961.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>9374723094.8</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>9374723094.799999</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>5390815186.5</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>2722439698.1</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>2722439698.1</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23920,10 @@
           <t>1918555066.051131</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>12847401961</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>12847401961.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24089,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24273,11 @@
           <t>46.94</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>43.19</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>40.9</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>43.19</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>40.9</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24324,16 @@
           <t>17904603214.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>7326001062.4</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>7326001062.4</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>4299803431.4</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>2525457286.94</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>2525457286.94</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24350,10 @@
           <t>1651790443.45904</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>17904603214</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>17904603214.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24519,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24703,11 @@
           <t>44.51000000000001</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>42.52</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>40.69</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>42.52</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>40.69</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24754,16 @@
           <t>8385497650.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>3945941494.4</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>3945941494.4</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>2599113437.9</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>2229827006.08</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>2229827006.08</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24780,10 @@
           <t>669862618.2396603</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>8385497650</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>8385497650.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
